--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>85.46855953101652</v>
+        <v>13.88864092379019</v>
       </c>
       <c r="D2" t="n">
-        <v>47.22475730927877</v>
+        <v>7.674023062757801</v>
       </c>
       <c r="E2" t="n">
-        <v>7.511499944835755</v>
+        <v>1.22061874103581</v>
       </c>
       <c r="F2" t="n">
-        <v>12.71625695632474</v>
+        <v>2.06639175540277</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.44555964134501</v>
+        <v>11.44740344171857</v>
       </c>
       <c r="D3" t="n">
-        <v>21.7922433966293</v>
+        <v>3.541239551952261</v>
       </c>
       <c r="E3" t="n">
-        <v>7.511499944835755</v>
+        <v>1.22061874103581</v>
       </c>
       <c r="F3" t="n">
-        <v>12.71625695632474</v>
+        <v>2.06639175540277</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
